--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21C.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21C.xlsx
@@ -103,28 +103,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/01/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/COBAT/transparencia/cuentapublica.html</t>
   </si>
   <si>
     <t>Departamento de Contabilidad</t>
   </si>
   <si>
-    <t>http://cobatlaxcala.edu.mx/portal/Transparencia/cuentapublica.html#</t>
-  </si>
-  <si>
-    <t>AD8B1664B195E609EF1EAD74C7275F51</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2022 al 31 de  marzo de 2022,   se informa que el Colegio de Bachilleres del Estado de Tlaxcala, emite la cuenta pública en forma trimestral en apego a lo establecido en los artículos 6 y 7 de la Ley de Fiscalización Superior para el Estado de Tlaxcala y sus Municipios de forma armonizada, dicha información se encuentra publicada en la página de internet  de esta institución educativa en el apartado de transparencia,  que comprende al ejercicio fiscal 2022.</t>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>118D0B88F4432CB8449B4835AA0108F1</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>02/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio  de 2023 al 30 de septiembre de 2023,   se informa que el Colegio de Bachilleres del Estado de Tlaxcala, emite la cuenta pública en forma trimestral en apego a lo establecido en los artículos 6 y 7 de la Ley de Fiscalización Superior y Rendición de Cuentas del Estado de Tlaxcala y sus Municipios, de forma armonizada, dicha información se encuentra publicada en la página de internet  de esta institución educativa en el apartado de transparencia,  que comprende al ejercicio fiscal 2023.</t>
   </si>
 </sst>
 </file>
@@ -524,7 +524,7 @@
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
@@ -661,22 +661,22 @@
     </row>
     <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>35</v>
